--- a/data/trans_dic/P1438_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1438_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,27</t>
+          <t>5,34; 8,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 12,71</t>
+          <t>8,91; 12,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 10,37</t>
+          <t>7,75; 10,07</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,34</t>
+          <t>3,39; 5,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,09</t>
+          <t>7,28; 9,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,03</t>
+          <t>5,68; 7,49</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,74</t>
+          <t>2,22; 4,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,83</t>
+          <t>6,11; 9,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,89</t>
+          <t>4,53; 6,42</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,7</t>
+          <t>3,24; 5,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,77</t>
+          <t>6,74; 9,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 6,89</t>
+          <t>5,35; 7,09</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,16</t>
+          <t>4,03; 5,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,38; 8,83</t>
+          <t>7,92; 9,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 6,82</t>
+          <t>6,17; 7,15</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45151</t>
+          <t>47768</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74310</t>
+          <t>77372</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119462</t>
+          <t>125140</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34961; 58876</t>
+          <t>36856; 61547</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63878; 85812</t>
+          <t>65259; 90325</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105370; 135927</t>
+          <t>110367; 143369</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>44342</t>
+          <t>47817</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>82863</t>
+          <t>91859</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127205</t>
+          <t>139676</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22739; 63714</t>
+          <t>35596; 62639</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69335; 96572</t>
+          <t>77889; 106874</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83850; 151192</t>
+          <t>120267; 158721</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>26030</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52714</t>
+          <t>61318</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75811</t>
+          <t>87348</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15076; 33210</t>
+          <t>17715; 37362</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25503; 73076</t>
+          <t>49510; 76875</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47332; 96320</t>
+          <t>72870; 103396</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>40137</t>
+          <t>42113</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79453</t>
+          <t>87785</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119590</t>
+          <t>129898</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30138; 52808</t>
+          <t>32126; 55089</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62137; 95754</t>
+          <t>75311; 104948</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100937; 139192</t>
+          <t>112766; 149509</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>152728</t>
+          <t>163729</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>289340</t>
+          <t>318334</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>442068</t>
+          <t>482063</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>118186; 178489</t>
+          <t>142231; 187382</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>233275; 322918</t>
+          <t>295366; 346789</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>382468; 485284</t>
+          <t>448195; 519194</t>
         </is>
       </c>
     </row>
